--- a/AAII_Financials/Yearly/MCHB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MCHB_YR_FIN.xlsx
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>642700</v>
+        <v>643600</v>
       </c>
       <c r="E8" s="3">
         <v>381600</v>
@@ -780,7 +780,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>642700</v>
+        <v>643600</v>
       </c>
       <c r="E10" s="3">
         <v>381600</v>
@@ -972,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>366600</v>
+        <v>367600</v>
       </c>
       <c r="E17" s="3">
         <v>315300</v>
